--- a/Дело3а-78-2026Таганай/06_Финансы/00_Ведомость_06_Финансовые_документы.xlsx
+++ b/Дело3а-78-2026Таганай/06_Финансы/00_Ведомость_06_Финансовые_документы.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ведомость 06" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ведомость 06'!$B$11:$H$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ведомость 06'!$B$11:$H$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Ведомость 06'!$1:$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+    <numFmt numFmtId="165" formatCode="dd.mm.yyyy"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -128,8 +128,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F4EC"/>
-        <bgColor rgb="00E8F4EC"/>
+        <fgColor rgb="00FFF6CC"/>
+        <bgColor rgb="00FFF6CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H47"/>
+  <dimension ref="B2:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -622,11 +622,11 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>4.13 МБ</t>
+          <t>4.12 МБ</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>46157.92963866661</v>
+        <v>46158.29719611591</v>
       </c>
     </row>
     <row r="9">
@@ -1516,81 +1516,50 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>06.28</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>Сводная ведомость</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>Сводная_ведомость.xlsx</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="n">
-        <v>46157.92521048632</v>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
-        <is>
-          <t>9 КБ</t>
-        </is>
-      </c>
-      <c r="G39" s="15" t="inlineStr"/>
-      <c r="H39" s="16" t="inlineStr">
-        <is>
-          <t>_____________</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="17" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>Председатель правления РКООИ ЦИП «Таганай»: Богдановский С.В.    ____________________</t>
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>Подсказки:</t>
+        </is>
+      </c>
+    </row>
     <row r="44">
-      <c r="B44" s="18" t="inlineStr">
-        <is>
-          <t>Подсказки:</t>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>• Колонка «Наименование документа» заполнена автоматически по имени файла — проверьте формулировки.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>• Колонка «Наименование документа» заполнена автоматически по имени файла — проверьте формулировки.</t>
+          <t>• Колонка «Стр.» (G) — для PDF укажите число страниц при необходимости.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="19" t="inlineStr">
         <is>
-          <t>• Колонка «Стр.» (G) — для PDF укажите число страниц при необходимости.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="19" t="inlineStr">
-        <is>
           <t>• Перезапуск скрипта перезапишет файл (в т.ч. наименования).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B11:H39"/>
+  <autoFilter ref="B11:H38"/>
   <mergeCells count="10">
     <mergeCell ref="E9:H9"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B47:H47"/>
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B42:H42"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="B45:H45"/>

--- a/Дело3а-78-2026Таганай/06_Финансы/00_Ведомость_06_Финансовые_документы.xlsx
+++ b/Дело3а-78-2026Таганай/06_Финансы/00_Ведомость_06_Финансовые_документы.xlsx
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>46158.29719611591</v>
+        <v>46158.37375884783</v>
       </c>
     </row>
     <row r="9">
